--- a/templates/launch-workbook/launch-workbook-template.xlsx
+++ b/templates/launch-workbook/launch-workbook-template.xlsx
@@ -1969,19 +1969,19 @@
         <v/>
       </c>
       <c r="B10">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
         <v/>
       </c>
       <c r="C10">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
         <v/>
       </c>
       <c r="D10">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
         <v/>
       </c>
       <c r="E10">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A10)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A10))</f>
         <v/>
       </c>
     </row>
@@ -1991,19 +1991,19 @@
         <v/>
       </c>
       <c r="B11">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
         <v/>
       </c>
       <c r="C11">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
         <v/>
       </c>
       <c r="D11">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
         <v/>
       </c>
       <c r="E11">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A11)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A11))</f>
         <v/>
       </c>
     </row>
@@ -2013,19 +2013,19 @@
         <v/>
       </c>
       <c r="B12">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
         <v/>
       </c>
       <c r="C12">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
         <v/>
       </c>
       <c r="D12">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
         <v/>
       </c>
       <c r="E12">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A12)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A12))</f>
         <v/>
       </c>
     </row>
@@ -2035,19 +2035,19 @@
         <v/>
       </c>
       <c r="B13">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
         <v/>
       </c>
       <c r="C13">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
         <v/>
       </c>
       <c r="D13">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
         <v/>
       </c>
       <c r="E13">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A13)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A13))</f>
         <v/>
       </c>
     </row>
@@ -2057,19 +2057,19 @@
         <v/>
       </c>
       <c r="B14">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
         <v/>
       </c>
       <c r="C14">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
         <v/>
       </c>
       <c r="D14">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
         <v/>
       </c>
       <c r="E14">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A14)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A14))</f>
         <v/>
       </c>
     </row>
@@ -2079,19 +2079,19 @@
         <v/>
       </c>
       <c r="B15">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
         <v/>
       </c>
       <c r="C15">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
         <v/>
       </c>
       <c r="D15">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
         <v/>
       </c>
       <c r="E15">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A15)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A15))</f>
         <v/>
       </c>
     </row>
@@ -2101,19 +2101,19 @@
         <v/>
       </c>
       <c r="B16">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
         <v/>
       </c>
       <c r="C16">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
         <v/>
       </c>
       <c r="D16">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
         <v/>
       </c>
       <c r="E16">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A16)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A16))</f>
         <v/>
       </c>
     </row>
@@ -2123,19 +2123,19 @@
         <v/>
       </c>
       <c r="B17">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
         <v/>
       </c>
       <c r="C17">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
         <v/>
       </c>
       <c r="D17">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
         <v/>
       </c>
       <c r="E17">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A17)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A17))</f>
         <v/>
       </c>
     </row>
@@ -2145,19 +2145,19 @@
         <v/>
       </c>
       <c r="B18">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
         <v/>
       </c>
       <c r="C18">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
         <v/>
       </c>
       <c r="D18">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
         <v/>
       </c>
       <c r="E18">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A18)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A18))</f>
         <v/>
       </c>
     </row>
@@ -2167,19 +2167,19 @@
         <v/>
       </c>
       <c r="B19">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
         <v/>
       </c>
       <c r="C19">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
         <v/>
       </c>
       <c r="D19">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
         <v/>
       </c>
       <c r="E19">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A19)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A19))</f>
         <v/>
       </c>
     </row>
@@ -2189,19 +2189,19 @@
         <v/>
       </c>
       <c r="B20">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
         <v/>
       </c>
       <c r="C20">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
         <v/>
       </c>
       <c r="D20">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
         <v/>
       </c>
       <c r="E20">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A20)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A20))</f>
         <v/>
       </c>
     </row>
@@ -2211,19 +2211,19 @@
         <v/>
       </c>
       <c r="B21">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
         <v/>
       </c>
       <c r="C21">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
         <v/>
       </c>
       <c r="D21">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
         <v/>
       </c>
       <c r="E21">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A21)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A21))</f>
         <v/>
       </c>
     </row>
@@ -2233,19 +2233,19 @@
         <v/>
       </c>
       <c r="B22">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
         <v/>
       </c>
       <c r="C22">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
         <v/>
       </c>
       <c r="D22">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
         <v/>
       </c>
       <c r="E22">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],$A22)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],$A22))</f>
         <v/>
       </c>
     </row>
@@ -2256,19 +2256,19 @@
         </is>
       </c>
       <c r="B23">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
         <v/>
       </c>
       <c r="C23">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
         <v/>
       </c>
       <c r="D23">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
         <v/>
       </c>
       <c r="E23">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes",tblLines[Zone],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes",tblLines[Zone],""))</f>
         <v/>
       </c>
     </row>
@@ -2302,19 +2302,19 @@
         </is>
       </c>
       <c r="B25">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="C25">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="D25">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="E25">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
     </row>
@@ -2611,19 +2611,19 @@
         <v/>
       </c>
       <c r="B49">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A49))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A49))</f>
         <v/>
       </c>
       <c r="C49">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A49))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A49))</f>
         <v/>
       </c>
       <c r="D49">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A49))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A49))</f>
         <v/>
       </c>
       <c r="E49">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A49))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A49)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A49))</f>
         <v/>
       </c>
     </row>
@@ -2633,19 +2633,19 @@
         <v/>
       </c>
       <c r="B50">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A50))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A50))</f>
         <v/>
       </c>
       <c r="C50">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A50))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A50))</f>
         <v/>
       </c>
       <c r="D50">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A50))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A50))</f>
         <v/>
       </c>
       <c r="E50">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A50))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A50)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A50))</f>
         <v/>
       </c>
     </row>
@@ -2655,19 +2655,19 @@
         <v/>
       </c>
       <c r="B51">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A51))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A51))</f>
         <v/>
       </c>
       <c r="C51">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A51))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A51))</f>
         <v/>
       </c>
       <c r="D51">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A51))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A51))</f>
         <v/>
       </c>
       <c r="E51">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A51))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A51)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A51))</f>
         <v/>
       </c>
     </row>
@@ -2677,19 +2677,19 @@
         <v/>
       </c>
       <c r="B52">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A52))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A52))</f>
         <v/>
       </c>
       <c r="C52">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A52))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A52))</f>
         <v/>
       </c>
       <c r="D52">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A52))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A52))</f>
         <v/>
       </c>
       <c r="E52">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A52))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A52)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A52))</f>
         <v/>
       </c>
     </row>
@@ -2699,19 +2699,19 @@
         <v/>
       </c>
       <c r="B53">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A53))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A53))</f>
         <v/>
       </c>
       <c r="C53">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A53))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A53))</f>
         <v/>
       </c>
       <c r="D53">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A53))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A53))</f>
         <v/>
       </c>
       <c r="E53">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A53))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A53)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A53))</f>
         <v/>
       </c>
     </row>
@@ -2721,19 +2721,19 @@
         <v/>
       </c>
       <c r="B54">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A54))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A54))</f>
         <v/>
       </c>
       <c r="C54">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A54))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A54))</f>
         <v/>
       </c>
       <c r="D54">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A54))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A54))</f>
         <v/>
       </c>
       <c r="E54">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A54))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A54)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A54))</f>
         <v/>
       </c>
     </row>
@@ -2743,19 +2743,19 @@
         <v/>
       </c>
       <c r="B55">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],$A55))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],$A55))</f>
         <v/>
       </c>
       <c r="C55">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],$A55))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],$A55))</f>
         <v/>
       </c>
       <c r="D55">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],$A55))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],$A55))</f>
         <v/>
       </c>
       <c r="E55">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],$A55))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],$A55)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],$A55))</f>
         <v/>
       </c>
     </row>
@@ -2766,19 +2766,19 @@
         </is>
       </c>
       <c r="B56">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],""))</f>
         <v/>
       </c>
       <c r="C56">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],""))</f>
         <v/>
       </c>
       <c r="D56">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],""))</f>
         <v/>
       </c>
       <c r="E56">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],""))</f>
         <v/>
       </c>
     </row>
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="B57" s="2">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="C57" s="2">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="D57" s="2">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
       <c r="E57" s="2">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes"))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Listing],"Yes")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Listing],"Yes"))</f>
         <v/>
       </c>
     </row>
@@ -2834,19 +2834,19 @@
         <v/>
       </c>
       <c r="B60">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A60))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A60))</f>
         <v/>
       </c>
       <c r="C60">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A60))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A60))</f>
         <v/>
       </c>
       <c r="D60">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A60))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A60))</f>
         <v/>
       </c>
       <c r="E60">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A60))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A60)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A60))</f>
         <v/>
       </c>
     </row>
@@ -2856,19 +2856,19 @@
         <v/>
       </c>
       <c r="B61">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A61))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A61))</f>
         <v/>
       </c>
       <c r="C61">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A61))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A61))</f>
         <v/>
       </c>
       <c r="D61">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A61))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A61))</f>
         <v/>
       </c>
       <c r="E61">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A61))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A61)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A61))</f>
         <v/>
       </c>
     </row>
@@ -2878,19 +2878,19 @@
         <v/>
       </c>
       <c r="B62">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A62))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A62))</f>
         <v/>
       </c>
       <c r="C62">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A62))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A62))</f>
         <v/>
       </c>
       <c r="D62">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A62))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A62))</f>
         <v/>
       </c>
       <c r="E62">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A62))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A62)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A62))</f>
         <v/>
       </c>
     </row>
@@ -2900,19 +2900,19 @@
         <v/>
       </c>
       <c r="B63">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A63))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A63))</f>
         <v/>
       </c>
       <c r="C63">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A63))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A63))</f>
         <v/>
       </c>
       <c r="D63">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A63))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A63))</f>
         <v/>
       </c>
       <c r="E63">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A63))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A63)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A63))</f>
         <v/>
       </c>
     </row>
@@ -2922,19 +2922,19 @@
         <v/>
       </c>
       <c r="B64">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A64))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A64))</f>
         <v/>
       </c>
       <c r="C64">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A64))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A64))</f>
         <v/>
       </c>
       <c r="D64">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A64))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A64))</f>
         <v/>
       </c>
       <c r="E64">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A64))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A64)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A64))</f>
         <v/>
       </c>
     </row>
@@ -2944,19 +2944,19 @@
         <v/>
       </c>
       <c r="B65">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A65))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A65))</f>
         <v/>
       </c>
       <c r="C65">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A65))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A65))</f>
         <v/>
       </c>
       <c r="D65">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A65))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A65))</f>
         <v/>
       </c>
       <c r="E65">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A65))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A65)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A65))</f>
         <v/>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         <v/>
       </c>
       <c r="B66">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A66))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A66))</f>
         <v/>
       </c>
       <c r="C66">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A66))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A66))</f>
         <v/>
       </c>
       <c r="D66">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A66))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A66))</f>
         <v/>
       </c>
       <c r="E66">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A66))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A66)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A66))</f>
         <v/>
       </c>
     </row>
@@ -2988,19 +2988,19 @@
         <v/>
       </c>
       <c r="B67">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A67))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A67))</f>
         <v/>
       </c>
       <c r="C67">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A67))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A67))</f>
         <v/>
       </c>
       <c r="D67">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A67))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A67))</f>
         <v/>
       </c>
       <c r="E67">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A67))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A67)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A67))</f>
         <v/>
       </c>
     </row>
@@ -3010,19 +3010,19 @@
         <v/>
       </c>
       <c r="B68">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],$A68))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],$A68))</f>
         <v/>
       </c>
       <c r="C68">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],$A68))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],$A68))</f>
         <v/>
       </c>
       <c r="D68">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],$A68))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],$A68))</f>
         <v/>
       </c>
       <c r="E68">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],$A68))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],$A68)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],$A68))</f>
         <v/>
       </c>
     </row>
@@ -3033,19 +3033,19 @@
         </is>
       </c>
       <c r="B69">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],""))</f>
         <v/>
       </c>
       <c r="C69">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],""))</f>
         <v/>
       </c>
       <c r="D69">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],""))</f>
         <v/>
       </c>
       <c r="E69">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],""))</f>
         <v/>
       </c>
     </row>
@@ -3056,19 +3056,19 @@
         </is>
       </c>
       <c r="B70" s="2">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Comms],"Sent"))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Comms],"Sent"))</f>
         <v/>
       </c>
       <c r="C70" s="2">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Comms],"Sent"))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Comms],"Sent"))</f>
         <v/>
       </c>
       <c r="D70" s="2">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Comms],"Sent"))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Comms],"Sent"))</f>
         <v/>
       </c>
       <c r="E70" s="2">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Comms],"Sent"))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Comms],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Comms],"Sent"))</f>
         <v/>
       </c>
     </row>
@@ -3101,19 +3101,19 @@
         <v/>
       </c>
       <c r="B73">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Floor plan],$A73))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Floor plan],$A73))</f>
         <v/>
       </c>
       <c r="C73">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Floor plan],$A73))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Floor plan],$A73))</f>
         <v/>
       </c>
       <c r="D73">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Floor plan],$A73))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Floor plan],$A73))</f>
         <v/>
       </c>
       <c r="E73">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Floor plan],$A73))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Floor plan],$A73)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Floor plan],$A73))</f>
         <v/>
       </c>
     </row>
@@ -3123,19 +3123,19 @@
         <v/>
       </c>
       <c r="B74">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Floor plan],$A74))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Floor plan],$A74))</f>
         <v/>
       </c>
       <c r="C74">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Floor plan],$A74))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Floor plan],$A74))</f>
         <v/>
       </c>
       <c r="D74">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Floor plan],$A74))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Floor plan],$A74))</f>
         <v/>
       </c>
       <c r="E74">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Floor plan],$A74))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Floor plan],$A74)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Floor plan],$A74))</f>
         <v/>
       </c>
     </row>
@@ -3146,19 +3146,19 @@
         </is>
       </c>
       <c r="B75">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Floor plan],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Floor plan],""))</f>
         <v/>
       </c>
       <c r="C75">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Floor plan],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Floor plan],""))</f>
         <v/>
       </c>
       <c r="D75">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Floor plan],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Floor plan],""))</f>
         <v/>
       </c>
       <c r="E75">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Floor plan],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Floor plan],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Floor plan],""))</f>
         <v/>
       </c>
     </row>
@@ -3169,19 +3169,19 @@
         </is>
       </c>
       <c r="B76" s="2">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 Floor plan],"Sent"))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 Floor plan],"Sent"))</f>
         <v/>
       </c>
       <c r="C76" s="2">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 Floor plan],"Sent"))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 Floor plan],"Sent"))</f>
         <v/>
       </c>
       <c r="D76" s="2">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 Floor plan],"Sent"))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 Floor plan],"Sent"))</f>
         <v/>
       </c>
       <c r="E76" s="2">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 Floor plan],"Sent"))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 Floor plan],"Sent")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 Floor plan],"Sent"))</f>
         <v/>
       </c>
     </row>
@@ -3214,19 +3214,19 @@
         <v/>
       </c>
       <c r="B79">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A79))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A79))</f>
         <v/>
       </c>
       <c r="C79">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A79))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A79))</f>
         <v/>
       </c>
       <c r="D79">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A79))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A79))</f>
         <v/>
       </c>
       <c r="E79">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A79))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A79)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A79))</f>
         <v/>
       </c>
     </row>
@@ -3236,19 +3236,19 @@
         <v/>
       </c>
       <c r="B80">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A80))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A80))</f>
         <v/>
       </c>
       <c r="C80">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A80))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A80))</f>
         <v/>
       </c>
       <c r="D80">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A80))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A80))</f>
         <v/>
       </c>
       <c r="E80">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A80))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A80)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A80))</f>
         <v/>
       </c>
     </row>
@@ -3258,19 +3258,19 @@
         <v/>
       </c>
       <c r="B81">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A81))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A81))</f>
         <v/>
       </c>
       <c r="C81">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A81))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A81))</f>
         <v/>
       </c>
       <c r="D81">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A81))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A81))</f>
         <v/>
       </c>
       <c r="E81">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A81))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A81)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A81))</f>
         <v/>
       </c>
     </row>
@@ -3280,19 +3280,19 @@
         <v/>
       </c>
       <c r="B82">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A82))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A82))</f>
         <v/>
       </c>
       <c r="C82">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A82))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A82))</f>
         <v/>
       </c>
       <c r="D82">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A82))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A82))</f>
         <v/>
       </c>
       <c r="E82">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A82))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A82)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A82))</f>
         <v/>
       </c>
     </row>
@@ -3302,19 +3302,19 @@
         <v/>
       </c>
       <c r="B83">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A83))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A83))</f>
         <v/>
       </c>
       <c r="C83">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A83))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A83))</f>
         <v/>
       </c>
       <c r="D83">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A83))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A83))</f>
         <v/>
       </c>
       <c r="E83">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A83))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A83)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A83))</f>
         <v/>
       </c>
     </row>
@@ -3324,19 +3324,19 @@
         <v/>
       </c>
       <c r="B84">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A84))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A84))</f>
         <v/>
       </c>
       <c r="C84">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A84))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A84))</f>
         <v/>
       </c>
       <c r="D84">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A84))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A84))</f>
         <v/>
       </c>
       <c r="E84">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A84))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A84)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A84))</f>
         <v/>
       </c>
     </row>
@@ -3346,19 +3346,19 @@
         <v/>
       </c>
       <c r="B85">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A85))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A85))</f>
         <v/>
       </c>
       <c r="C85">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A85))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A85))</f>
         <v/>
       </c>
       <c r="D85">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A85))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A85))</f>
         <v/>
       </c>
       <c r="E85">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A85))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A85)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A85))</f>
         <v/>
       </c>
     </row>
@@ -3368,19 +3368,19 @@
         <v/>
       </c>
       <c r="B86">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A86))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A86))</f>
         <v/>
       </c>
       <c r="C86">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A86))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A86))</f>
         <v/>
       </c>
       <c r="D86">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A86))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A86))</f>
         <v/>
       </c>
       <c r="E86">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A86))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A86)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A86))</f>
         <v/>
       </c>
     </row>
@@ -3390,19 +3390,19 @@
         <v/>
       </c>
       <c r="B87">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],$A87))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],$A87))</f>
         <v/>
       </c>
       <c r="C87">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],$A87))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],$A87))</f>
         <v/>
       </c>
       <c r="D87">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],$A87))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],$A87))</f>
         <v/>
       </c>
       <c r="E87">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],$A87))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],$A87)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],$A87))</f>
         <v/>
       </c>
     </row>
@@ -3413,19 +3413,19 @@
         </is>
       </c>
       <c r="B88">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],""))</f>
         <v/>
       </c>
       <c r="C88">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],""))</f>
         <v/>
       </c>
       <c r="D88">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],""))</f>
         <v/>
       </c>
       <c r="E88">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],""))</f>
         <v/>
       </c>
     </row>
@@ -3436,19 +3436,19 @@
         </is>
       </c>
       <c r="B89" s="2">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 PO],"Picked at US DC"))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 PO],"Picked at US DC"))</f>
         <v/>
       </c>
       <c r="C89" s="2">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 PO],"Picked at US DC"))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 PO],"Picked at US DC"))</f>
         <v/>
       </c>
       <c r="D89" s="2">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 PO],"Picked at US DC"))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 PO],"Picked at US DC"))</f>
         <v/>
       </c>
       <c r="E89" s="2">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 PO],"Picked at US DC"))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 PO],"Picked at US DC")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],"Released")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 PO],"Picked at US DC"))</f>
         <v/>
       </c>
     </row>
@@ -3481,19 +3481,19 @@
         <v/>
       </c>
       <c r="B92">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A92))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A92))</f>
         <v/>
       </c>
       <c r="C92">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A92))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A92))</f>
         <v/>
       </c>
       <c r="D92">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A92))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A92))</f>
         <v/>
       </c>
       <c r="E92">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A92))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A92)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A92))</f>
         <v/>
       </c>
     </row>
@@ -3503,19 +3503,19 @@
         <v/>
       </c>
       <c r="B93">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A93))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A93))</f>
         <v/>
       </c>
       <c r="C93">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A93))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A93))</f>
         <v/>
       </c>
       <c r="D93">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A93))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A93))</f>
         <v/>
       </c>
       <c r="E93">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A93))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A93)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A93))</f>
         <v/>
       </c>
     </row>
@@ -3525,19 +3525,19 @@
         <v/>
       </c>
       <c r="B94">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A94))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A94))</f>
         <v/>
       </c>
       <c r="C94">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A94))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A94))</f>
         <v/>
       </c>
       <c r="D94">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A94))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A94))</f>
         <v/>
       </c>
       <c r="E94">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A94))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A94)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A94))</f>
         <v/>
       </c>
     </row>
@@ -3547,19 +3547,19 @@
         <v/>
       </c>
       <c r="B95">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A95))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A95))</f>
         <v/>
       </c>
       <c r="C95">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A95))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A95))</f>
         <v/>
       </c>
       <c r="D95">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A95))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A95))</f>
         <v/>
       </c>
       <c r="E95">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A95))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A95)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A95))</f>
         <v/>
       </c>
     </row>
@@ -3569,19 +3569,19 @@
         <v/>
       </c>
       <c r="B96">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A96))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A96))</f>
         <v/>
       </c>
       <c r="C96">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A96))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A96))</f>
         <v/>
       </c>
       <c r="D96">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A96))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A96))</f>
         <v/>
       </c>
       <c r="E96">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A96))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A96)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A96))</f>
         <v/>
       </c>
     </row>
@@ -3591,19 +3591,19 @@
         <v/>
       </c>
       <c r="B97">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A97))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A97))</f>
         <v/>
       </c>
       <c r="C97">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A97))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A97))</f>
         <v/>
       </c>
       <c r="D97">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A97))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A97))</f>
         <v/>
       </c>
       <c r="E97">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A97))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A97)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A97))</f>
         <v/>
       </c>
     </row>
@@ -3613,19 +3613,19 @@
         <v/>
       </c>
       <c r="B98">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A98))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A98))</f>
         <v/>
       </c>
       <c r="C98">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A98))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A98))</f>
         <v/>
       </c>
       <c r="D98">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A98))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A98))</f>
         <v/>
       </c>
       <c r="E98">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A98))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A98)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A98))</f>
         <v/>
       </c>
     </row>
@@ -3635,19 +3635,19 @@
         <v/>
       </c>
       <c r="B99">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A99))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A99))</f>
         <v/>
       </c>
       <c r="C99">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A99))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A99))</f>
         <v/>
       </c>
       <c r="D99">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A99))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A99))</f>
         <v/>
       </c>
       <c r="E99">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A99))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A99)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A99))</f>
         <v/>
       </c>
     </row>
@@ -3657,19 +3657,19 @@
         <v/>
       </c>
       <c r="B100">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],$A100))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],$A100))</f>
         <v/>
       </c>
       <c r="C100">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],$A100))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],$A100))</f>
         <v/>
       </c>
       <c r="D100">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],$A100))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],$A100))</f>
         <v/>
       </c>
       <c r="E100">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],$A100))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],$A100)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],$A100))</f>
         <v/>
       </c>
     </row>
@@ -3680,19 +3680,19 @@
         </is>
       </c>
       <c r="B101">
-        <f>IF(B$5="","",COUNTIFS(tblLines[Store 1],B$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Store 2],B$5,tblLines[S2 At launch],""))</f>
+        <f>IF(B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],B$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],B$5,tblLines[S2 At launch],""))</f>
         <v/>
       </c>
       <c r="C101">
-        <f>IF(C$5="","",COUNTIFS(tblLines[Store 1],C$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Store 2],C$5,tblLines[S2 At launch],""))</f>
+        <f>IF(C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],C$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],C$5,tblLines[S2 At launch],""))</f>
         <v/>
       </c>
       <c r="D101">
-        <f>IF(D$5="","",COUNTIFS(tblLines[Store 1],D$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Store 2],D$5,tblLines[S2 At launch],""))</f>
+        <f>IF(D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],D$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],D$5,tblLines[S2 At launch],""))</f>
         <v/>
       </c>
       <c r="E101">
-        <f>IF(E$5="","",COUNTIFS(tblLines[Store 1],E$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Store 2],E$5,tblLines[S2 At launch],""))</f>
+        <f>IF(E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],E$5,tblLines[S1 At launch],"")+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],E$5,tblLines[S2 At launch],""))</f>
         <v/>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         <v/>
       </c>
       <c r="C199">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A199))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A199))</f>
         <v/>
       </c>
       <c r="D199">
@@ -4999,7 +4999,7 @@
         <v/>
       </c>
       <c r="E199">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A199))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A199))</f>
         <v/>
       </c>
       <c r="F199">
@@ -5007,7 +5007,7 @@
         <v/>
       </c>
       <c r="G199">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A199))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A199))</f>
         <v/>
       </c>
       <c r="H199">
@@ -5015,7 +5015,7 @@
         <v/>
       </c>
       <c r="I199">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A199))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A199)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A199))</f>
         <v/>
       </c>
     </row>
@@ -5029,7 +5029,7 @@
         <v/>
       </c>
       <c r="C200">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A200))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A200))</f>
         <v/>
       </c>
       <c r="D200">
@@ -5037,7 +5037,7 @@
         <v/>
       </c>
       <c r="E200">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A200))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A200))</f>
         <v/>
       </c>
       <c r="F200">
@@ -5045,7 +5045,7 @@
         <v/>
       </c>
       <c r="G200">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A200))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A200))</f>
         <v/>
       </c>
       <c r="H200">
@@ -5053,7 +5053,7 @@
         <v/>
       </c>
       <c r="I200">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A200))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A200)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A200))</f>
         <v/>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
         <v/>
       </c>
       <c r="C201">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A201))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A201))</f>
         <v/>
       </c>
       <c r="D201">
@@ -5075,7 +5075,7 @@
         <v/>
       </c>
       <c r="E201">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A201))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A201))</f>
         <v/>
       </c>
       <c r="F201">
@@ -5083,7 +5083,7 @@
         <v/>
       </c>
       <c r="G201">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A201))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A201))</f>
         <v/>
       </c>
       <c r="H201">
@@ -5091,7 +5091,7 @@
         <v/>
       </c>
       <c r="I201">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A201))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A201)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A201))</f>
         <v/>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
         <v/>
       </c>
       <c r="C202">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A202))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A202))</f>
         <v/>
       </c>
       <c r="D202">
@@ -5113,7 +5113,7 @@
         <v/>
       </c>
       <c r="E202">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A202))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A202))</f>
         <v/>
       </c>
       <c r="F202">
@@ -5121,7 +5121,7 @@
         <v/>
       </c>
       <c r="G202">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A202))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A202))</f>
         <v/>
       </c>
       <c r="H202">
@@ -5129,7 +5129,7 @@
         <v/>
       </c>
       <c r="I202">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A202))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A202)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A202))</f>
         <v/>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
         <v/>
       </c>
       <c r="C203">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A203))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A203))</f>
         <v/>
       </c>
       <c r="D203">
@@ -5151,7 +5151,7 @@
         <v/>
       </c>
       <c r="E203">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A203))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A203))</f>
         <v/>
       </c>
       <c r="F203">
@@ -5159,7 +5159,7 @@
         <v/>
       </c>
       <c r="G203">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A203))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A203))</f>
         <v/>
       </c>
       <c r="H203">
@@ -5167,7 +5167,7 @@
         <v/>
       </c>
       <c r="I203">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A203))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A203)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A203))</f>
         <v/>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v/>
       </c>
       <c r="C204">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A204))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A204))</f>
         <v/>
       </c>
       <c r="D204">
@@ -5189,7 +5189,7 @@
         <v/>
       </c>
       <c r="E204">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A204))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A204))</f>
         <v/>
       </c>
       <c r="F204">
@@ -5197,7 +5197,7 @@
         <v/>
       </c>
       <c r="G204">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A204))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A204))</f>
         <v/>
       </c>
       <c r="H204">
@@ -5205,7 +5205,7 @@
         <v/>
       </c>
       <c r="I204">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A204))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A204)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A204))</f>
         <v/>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         <v/>
       </c>
       <c r="C205">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A205))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A205))</f>
         <v/>
       </c>
       <c r="D205">
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="E205">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A205))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A205))</f>
         <v/>
       </c>
       <c r="F205">
@@ -5235,7 +5235,7 @@
         <v/>
       </c>
       <c r="G205">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A205))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A205))</f>
         <v/>
       </c>
       <c r="H205">
@@ -5243,7 +5243,7 @@
         <v/>
       </c>
       <c r="I205">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A205))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A205)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A205))</f>
         <v/>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
         <v/>
       </c>
       <c r="C206">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A206))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A206))</f>
         <v/>
       </c>
       <c r="D206">
@@ -5265,7 +5265,7 @@
         <v/>
       </c>
       <c r="E206">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A206))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A206))</f>
         <v/>
       </c>
       <c r="F206">
@@ -5273,7 +5273,7 @@
         <v/>
       </c>
       <c r="G206">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A206))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A206))</f>
         <v/>
       </c>
       <c r="H206">
@@ -5281,7 +5281,7 @@
         <v/>
       </c>
       <c r="I206">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A206))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A206)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A206))</f>
         <v/>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
         <v/>
       </c>
       <c r="C207">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A207))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A207))</f>
         <v/>
       </c>
       <c r="D207">
@@ -5303,7 +5303,7 @@
         <v/>
       </c>
       <c r="E207">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A207))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A207))</f>
         <v/>
       </c>
       <c r="F207">
@@ -5311,7 +5311,7 @@
         <v/>
       </c>
       <c r="G207">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A207))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A207))</f>
         <v/>
       </c>
       <c r="H207">
@@ -5319,7 +5319,7 @@
         <v/>
       </c>
       <c r="I207">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A207))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A207)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A207))</f>
         <v/>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
         <v/>
       </c>
       <c r="C208">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A208))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A208))</f>
         <v/>
       </c>
       <c r="D208">
@@ -5341,7 +5341,7 @@
         <v/>
       </c>
       <c r="E208">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A208))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A208))</f>
         <v/>
       </c>
       <c r="F208">
@@ -5349,7 +5349,7 @@
         <v/>
       </c>
       <c r="G208">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A208))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A208))</f>
         <v/>
       </c>
       <c r="H208">
@@ -5357,7 +5357,7 @@
         <v/>
       </c>
       <c r="I208">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A208))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A208)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A208))</f>
         <v/>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
         <v/>
       </c>
       <c r="C209">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A209))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A209))</f>
         <v/>
       </c>
       <c r="D209">
@@ -5379,7 +5379,7 @@
         <v/>
       </c>
       <c r="E209">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A209))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A209))</f>
         <v/>
       </c>
       <c r="F209">
@@ -5387,7 +5387,7 @@
         <v/>
       </c>
       <c r="G209">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A209))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A209))</f>
         <v/>
       </c>
       <c r="H209">
@@ -5395,7 +5395,7 @@
         <v/>
       </c>
       <c r="I209">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A209))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A209)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A209))</f>
         <v/>
       </c>
     </row>
@@ -5409,7 +5409,7 @@
         <v/>
       </c>
       <c r="C210">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A210))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A210))</f>
         <v/>
       </c>
       <c r="D210">
@@ -5417,7 +5417,7 @@
         <v/>
       </c>
       <c r="E210">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A210))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A210))</f>
         <v/>
       </c>
       <c r="F210">
@@ -5425,7 +5425,7 @@
         <v/>
       </c>
       <c r="G210">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A210))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A210))</f>
         <v/>
       </c>
       <c r="H210">
@@ -5433,7 +5433,7 @@
         <v/>
       </c>
       <c r="I210">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A210))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A210)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A210))</f>
         <v/>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
         <v/>
       </c>
       <c r="C211">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A211))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A211))</f>
         <v/>
       </c>
       <c r="D211">
@@ -5455,7 +5455,7 @@
         <v/>
       </c>
       <c r="E211">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A211))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A211))</f>
         <v/>
       </c>
       <c r="F211">
@@ -5463,7 +5463,7 @@
         <v/>
       </c>
       <c r="G211">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A211))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A211))</f>
         <v/>
       </c>
       <c r="H211">
@@ -5471,7 +5471,7 @@
         <v/>
       </c>
       <c r="I211">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A211))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A211)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A211))</f>
         <v/>
       </c>
     </row>
@@ -5485,7 +5485,7 @@
         <v/>
       </c>
       <c r="C212">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A212))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A212))</f>
         <v/>
       </c>
       <c r="D212">
@@ -5493,7 +5493,7 @@
         <v/>
       </c>
       <c r="E212">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A212))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A212))</f>
         <v/>
       </c>
       <c r="F212">
@@ -5501,7 +5501,7 @@
         <v/>
       </c>
       <c r="G212">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A212))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A212))</f>
         <v/>
       </c>
       <c r="H212">
@@ -5509,7 +5509,7 @@
         <v/>
       </c>
       <c r="I212">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A212))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A212)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A212))</f>
         <v/>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
         <v/>
       </c>
       <c r="C213">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A213))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A213))</f>
         <v/>
       </c>
       <c r="D213">
@@ -5531,7 +5531,7 @@
         <v/>
       </c>
       <c r="E213">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A213))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A213))</f>
         <v/>
       </c>
       <c r="F213">
@@ -5539,7 +5539,7 @@
         <v/>
       </c>
       <c r="G213">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A213))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A213))</f>
         <v/>
       </c>
       <c r="H213">
@@ -5547,7 +5547,7 @@
         <v/>
       </c>
       <c r="I213">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A213))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A213)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A213))</f>
         <v/>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
         <v/>
       </c>
       <c r="C214">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A214))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A214))</f>
         <v/>
       </c>
       <c r="D214">
@@ -5569,7 +5569,7 @@
         <v/>
       </c>
       <c r="E214">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A214))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A214))</f>
         <v/>
       </c>
       <c r="F214">
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="G214">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A214))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A214))</f>
         <v/>
       </c>
       <c r="H214">
@@ -5585,7 +5585,7 @@
         <v/>
       </c>
       <c r="I214">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A214))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A214)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A214))</f>
         <v/>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
         <v/>
       </c>
       <c r="C215">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A215))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A215))</f>
         <v/>
       </c>
       <c r="D215">
@@ -5607,7 +5607,7 @@
         <v/>
       </c>
       <c r="E215">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A215))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A215))</f>
         <v/>
       </c>
       <c r="F215">
@@ -5615,7 +5615,7 @@
         <v/>
       </c>
       <c r="G215">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A215))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A215))</f>
         <v/>
       </c>
       <c r="H215">
@@ -5623,7 +5623,7 @@
         <v/>
       </c>
       <c r="I215">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A215))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A215)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A215))</f>
         <v/>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         <v/>
       </c>
       <c r="C216">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A216))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A216))</f>
         <v/>
       </c>
       <c r="D216">
@@ -5645,7 +5645,7 @@
         <v/>
       </c>
       <c r="E216">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A216))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A216))</f>
         <v/>
       </c>
       <c r="F216">
@@ -5653,7 +5653,7 @@
         <v/>
       </c>
       <c r="G216">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A216))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A216))</f>
         <v/>
       </c>
       <c r="H216">
@@ -5661,7 +5661,7 @@
         <v/>
       </c>
       <c r="I216">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A216))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A216)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A216))</f>
         <v/>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
         <v/>
       </c>
       <c r="C217">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A217))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A217))</f>
         <v/>
       </c>
       <c r="D217">
@@ -5683,7 +5683,7 @@
         <v/>
       </c>
       <c r="E217">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A217))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A217))</f>
         <v/>
       </c>
       <c r="F217">
@@ -5691,7 +5691,7 @@
         <v/>
       </c>
       <c r="G217">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A217))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A217))</f>
         <v/>
       </c>
       <c r="H217">
@@ -5699,7 +5699,7 @@
         <v/>
       </c>
       <c r="I217">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A217))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A217)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A217))</f>
         <v/>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
         <v/>
       </c>
       <c r="C218">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A218))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A218))</f>
         <v/>
       </c>
       <c r="D218">
@@ -5721,7 +5721,7 @@
         <v/>
       </c>
       <c r="E218">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A218))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A218))</f>
         <v/>
       </c>
       <c r="F218">
@@ -5729,7 +5729,7 @@
         <v/>
       </c>
       <c r="G218">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A218))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A218))</f>
         <v/>
       </c>
       <c r="H218">
@@ -5737,7 +5737,7 @@
         <v/>
       </c>
       <c r="I218">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A218))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A218)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A218))</f>
         <v/>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
         <v/>
       </c>
       <c r="C219">
-        <f>IF($B$5="","",COUNTIFS(tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A219))</f>
+        <f>IF($B$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$B$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$B$5,tblLines[S2 Fixture type],$A219))</f>
         <v/>
       </c>
       <c r="D219">
@@ -5759,7 +5759,7 @@
         <v/>
       </c>
       <c r="E219">
-        <f>IF($C$5="","",COUNTIFS(tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A219))</f>
+        <f>IF($C$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$C$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$C$5,tblLines[S2 Fixture type],$A219))</f>
         <v/>
       </c>
       <c r="F219">
@@ -5767,7 +5767,7 @@
         <v/>
       </c>
       <c r="G219">
-        <f>IF($D$5="","",COUNTIFS(tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A219))</f>
+        <f>IF($D$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$D$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$D$5,tblLines[S2 Fixture type],$A219))</f>
         <v/>
       </c>
       <c r="H219">
@@ -5775,17 +5775,17 @@
         <v/>
       </c>
       <c r="I219">
-        <f>IF($E$5="","",COUNTIFS(tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A219))</f>
+        <f>IF($E$5="","",COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 1],$E$5,tblLines[S1 Fixture type],$A219)+COUNTIFS(tblLines[Launch],$B$4,tblLines[Store 2],$E$5,tblLines[S2 Fixture type],$A219))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=lst_Launch</formula1>
+      <formula1>lst_Launch</formula1>
     </dataValidation>
     <dataValidation sqref="B5:E5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7872,43 +7872,43 @@
   </conditionalFormatting>
   <dataValidations count="54">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Launch" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Launch</formula1>
+      <formula1>lst_Launch</formula1>
     </dataValidation>
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Main category" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_MainCategory</formula1>
+      <formula1>lst_MainCategory</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Zone" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Zone</formula1>
+      <formula1>lst_Zone</formula1>
     </dataValidation>
     <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Area" error="Enter a valid value." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Brand team" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_BrandTeam</formula1>
+      <formula1>lst_BrandTeam</formula1>
     </dataValidation>
     <dataValidation sqref="J5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Brand code" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_BrandCode</formula1>
+      <formula1>lst_BrandCode</formula1>
     </dataValidation>
     <dataValidation sqref="K5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Double placement" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="L5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Brand" error="Pick a value from the list (Lists sheet)." type="list" errorStyle="warning">
-      <formula1>=lst_Brand</formula1>
+      <formula1>lst_Brand</formula1>
     </dataValidation>
     <dataValidation sqref="N5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="From" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Origin</formula1>
+      <formula1>lst_Origin</formula1>
     </dataValidation>
     <dataValidation sqref="O5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Market status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_MarketStatus</formula1>
+      <formula1>lst_MarketStatus</formula1>
     </dataValidation>
     <dataValidation sqref="P5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Internal category" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_InternalCategory</formula1>
+      <formula1>lst_InternalCategory</formula1>
     </dataValidation>
     <dataValidation sqref="Q5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="The 80 brands" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="R5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marketing OK" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_MarketingOK</formula1>
+      <formula1>lst_MarketingOK</formula1>
     </dataValidation>
     <dataValidation sqref="S5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Penetration plan" error="Enter a valid value." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -7923,25 +7923,25 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="X5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Store 1" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
     <dataValidation sqref="Y5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Listing" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Listing</formula1>
+      <formula1>lst_Listing</formula1>
     </dataValidation>
     <dataValidation sqref="Z5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 At launch" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_AtLaunch</formula1>
+      <formula1>lst_AtLaunch</formula1>
     </dataValidation>
     <dataValidation sqref="AA5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 At launch recheck" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_AtLaunch</formula1>
+      <formula1>lst_AtLaunch</formula1>
     </dataValidation>
     <dataValidation sqref="AB5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Comms" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Comms</formula1>
+      <formula1>lst_Comms</formula1>
     </dataValidation>
     <dataValidation sqref="AC5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Floor plan" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FloorPlan</formula1>
+      <formula1>lst_FloorPlan</formula1>
     </dataValidation>
     <dataValidation sqref="AE5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Fixture type" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FixtureType</formula1>
+      <formula1>lst_FixtureType</formula1>
     </dataValidation>
     <dataValidation sqref="AF5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Width ft" error="Enter a valid value." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -7950,31 +7950,31 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="AH5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 Temporary" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="AI5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S1 PO" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_PO</formula1>
+      <formula1>lst_PO</formula1>
     </dataValidation>
     <dataValidation sqref="AJ5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Store 2" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
     <dataValidation sqref="AK5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Listing" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Listing</formula1>
+      <formula1>lst_Listing</formula1>
     </dataValidation>
     <dataValidation sqref="AL5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 At launch" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_AtLaunch</formula1>
+      <formula1>lst_AtLaunch</formula1>
     </dataValidation>
     <dataValidation sqref="AM5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 At launch recheck" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_AtLaunch</formula1>
+      <formula1>lst_AtLaunch</formula1>
     </dataValidation>
     <dataValidation sqref="AN5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Comms" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Comms</formula1>
+      <formula1>lst_Comms</formula1>
     </dataValidation>
     <dataValidation sqref="AO5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Floor plan" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FloorPlan</formula1>
+      <formula1>lst_FloorPlan</formula1>
     </dataValidation>
     <dataValidation sqref="AQ5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Fixture type" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FixtureType</formula1>
+      <formula1>lst_FixtureType</formula1>
     </dataValidation>
     <dataValidation sqref="AR5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Width ft" error="Enter a valid value." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -7983,55 +7983,55 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="AT5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 Temporary" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="AU5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="S2 PO" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_PO</formula1>
+      <formula1>lst_PO</formula1>
     </dataValidation>
     <dataValidation sqref="AV5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="VPA status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_VPA</formula1>
+      <formula1>lst_VPA</formula1>
     </dataValidation>
     <dataValidation sqref="AW5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="VPA shared" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNoTBC</formula1>
+      <formula1>lst_YesNoTBC</formula1>
     </dataValidation>
     <dataValidation sqref="AX5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="VPA countersigned" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="AY5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="VPA signed" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNoTBC</formula1>
+      <formula1>lst_YesNoTBC</formula1>
     </dataValidation>
     <dataValidation sqref="AZ5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Data set-up" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Registration</formula1>
+      <formula1>lst_Registration</formula1>
     </dataValidation>
     <dataValidation sqref="BA5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Data set-up quarter" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Quarter</formula1>
+      <formula1>lst_Quarter</formula1>
     </dataValidation>
     <dataValidation sqref="BB5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Project comms" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_ProjectComms</formula1>
+      <formula1>lst_ProjectComms</formula1>
     </dataValidation>
     <dataValidation sqref="BC5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Schematics" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Schematics</formula1>
+      <formula1>lst_Schematics</formula1>
     </dataValidation>
     <dataValidation sqref="BD5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Schematics same as" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_StoreOrMarket</formula1>
+      <formula1>lst_StoreOrMarket</formula1>
     </dataValidation>
     <dataValidation sqref="BE5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Vendor set-up route" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_VendorRoute</formula1>
+      <formula1>lst_VendorRoute</formula1>
     </dataValidation>
     <dataValidation sqref="BF5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Vendor set-up state" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_VendorState</formula1>
+      <formula1>lst_VendorState</formula1>
     </dataValidation>
     <dataValidation sqref="BH5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="ICF" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_ICF</formula1>
+      <formula1>lst_ICF</formula1>
     </dataValidation>
     <dataValidation sqref="BI5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Supplier opening form" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_SupplierForm</formula1>
+      <formula1>lst_SupplierForm</formula1>
     </dataValidation>
     <dataValidation sqref="BJ5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Account opening form" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_AccountForm</formula1>
+      <formula1>lst_AccountForm</formula1>
     </dataValidation>
     <dataValidation sqref="BK5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Order shared" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_OrderShared</formula1>
+      <formula1>lst_OrderShared</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8121,7 +8121,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="New brand" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8262,16 +8262,16 @@
   </sheetData>
   <dataValidations count="9">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Brand" error="Pick a value from the list (Lists sheet)." type="list" errorStyle="warning">
-      <formula1>=lst_Brand</formula1>
+      <formula1>lst_Brand</formula1>
     </dataValidation>
     <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Market" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Market</formula1>
+      <formula1>lst_Market</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Distribution status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_DistStatus</formula1>
+      <formula1>lst_DistStatus</formula1>
     </dataValidation>
     <dataValidation sqref="E5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Distributor" error="Pick a value from the list (Lists sheet)." type="list" errorStyle="warning">
-      <formula1>=lst_Vendor</formula1>
+      <formula1>lst_Vendor</formula1>
     </dataValidation>
     <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Margin" error="Enter a valid value." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -8280,13 +8280,13 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="L5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Exclusive" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Exclusivity</formula1>
+      <formula1>lst_Exclusivity</formula1>
     </dataValidation>
     <dataValidation sqref="M5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Exclusive months" error="Enter a valid value." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="N5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Registration route" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_RegRoute</formula1>
+      <formula1>lst_RegRoute</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8493,10 +8493,10 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="F5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Vendor" error="Pick a value from the list (Lists sheet)." type="list" errorStyle="warning">
-      <formula1>=lst_Vendor</formula1>
+      <formula1>lst_Vendor</formula1>
     </dataValidation>
     <dataValidation sqref="G5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Market" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Market</formula1>
+      <formula1>lst_Market</formula1>
     </dataValidation>
     <dataValidation sqref="J5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Lines" error="Enter a valid value." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -8712,31 +8712,31 @@
   </sheetData>
   <dataValidations count="12">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Market" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Market</formula1>
+      <formula1>lst_Market</formula1>
     </dataValidation>
     <dataValidation sqref="H5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Market" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Market</formula1>
+      <formula1>lst_Market</formula1>
     </dataValidation>
     <dataValidation sqref="I5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Role" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_StoreRole</formula1>
+      <formula1>lst_StoreRole</formula1>
     </dataValidation>
     <dataValidation sqref="J5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Opening" error="Enter a valid value." type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
     <dataValidation sqref="N5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Store" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
     <dataValidation sqref="P5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fixture type" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FixtureType</formula1>
+      <formula1>lst_FixtureType</formula1>
     </dataValidation>
     <dataValidation sqref="Q5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Count" error="Enter a valid value." type="whole" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="V5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Store" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
     <dataValidation sqref="X5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fixture type" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_FixtureType</formula1>
+      <formula1>lst_FixtureType</formula1>
     </dataValidation>
     <dataValidation sqref="Y5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Width ft" error="Enter a valid value." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -8745,7 +8745,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="AA5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Temporary" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8925,13 +8925,13 @@
   </sheetData>
   <dataValidations count="11">
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Store" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_Store</formula1>
+      <formula1>lst_Store</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Vendor" error="Pick a value from the list (Lists sheet)." type="list" errorStyle="warning">
-      <formula1>=lst_Vendor</formula1>
+      <formula1>lst_Vendor</formula1>
     </dataValidation>
     <dataValidation sqref="I5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Same fixture as" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_StoreOrMarket</formula1>
+      <formula1>lst_StoreOrMarket</formula1>
     </dataValidation>
     <dataValidation sqref="K5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Install start" error="Enter a valid value." type="date" operator="greaterThan">
       <formula1>36526</formula1>
@@ -8940,19 +8940,19 @@
       <formula1>36526</formula1>
     </dataValidation>
     <dataValidation sqref="M5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Install status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_InstallStatus</formula1>
+      <formula1>lst_InstallStatus</formula1>
     </dataValidation>
     <dataValidation sqref="O5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Delivery date" error="Enter a valid value." type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
     <dataValidation sqref="P5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Delivery status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_DeliveryStatus</formula1>
+      <formula1>lst_DeliveryStatus</formula1>
     </dataValidation>
     <dataValidation sqref="Q5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="VM status" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_VMStatus</formula1>
+      <formula1>lst_VMStatus</formula1>
     </dataValidation>
     <dataValidation sqref="R5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Wall perimeter" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_YesNo</formula1>
+      <formula1>lst_YesNo</formula1>
     </dataValidation>
     <dataValidation sqref="S5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Email sent" error="Enter a valid value." type="date" operator="greaterThan">
       <formula1>36526</formula1>
@@ -9183,7 +9183,7 @@
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="A5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Type" error="Pick a value from the list (Lists sheet)." type="list">
-      <formula1>=lst_NPDType</formula1>
+      <formula1>lst_NPDType</formula1>
     </dataValidation>
     <dataValidation sqref="D5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Sizing sent" error="Enter a valid value." type="date" operator="greaterThan">
       <formula1>36526</formula1>
